--- a/output/full_scan/batch_seq1_2026-09-03.xlsx
+++ b/output/full_scan/batch_seq1_2026-09-03.xlsx
@@ -5043,7 +5043,7 @@
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>236.5275110955122</v>
+        <v>236.5275110955121</v>
       </c>
       <c r="E87" s="2" t="n">
         <v>10.05</v>
